--- a/myapp/src/assets/Asset72_T12_Template.xlsx
+++ b/myapp/src/assets/Asset72_T12_Template.xlsx
@@ -1,37 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriya.m\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1B8044-89E3-4CA4-94F5-E9E485872A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12 Upload" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="T12 Upload" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>Property Name</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Gross Potential Rent</t>
+  </si>
+  <si>
+    <t>Other Income</t>
+  </si>
+  <si>
+    <t>NOI</t>
+  </si>
+  <si>
+    <t>Concessions</t>
+  </si>
+  <si>
+    <t>Bad Debt</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Renting</t>
+  </si>
+  <si>
+    <t>Adminstrative</t>
+  </si>
+  <si>
+    <t>Maintenance Expenses</t>
+  </si>
+  <si>
+    <t>Payroll</t>
+  </si>
+  <si>
+    <t>Operating Expense</t>
+  </si>
+  <si>
+    <t>Grounds</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management </t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Professional fees</t>
+  </si>
+  <si>
+    <t>Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacancy </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,85 +136,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,64 +449,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Property Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Vacancy Loss</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Effective Gross Income</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>NOI</t>
-        </is>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
   </dataValidations>
